--- a/project/HW4/GUI_Checklist.xlsx
+++ b/project/HW4/GUI_Checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thanhthuy/Documents/Testing-PRJ-SM/project/HW4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35988B8E-F205-824E-AAED-F4C30675024E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2280B1-6FE5-A142-8A3D-072E4499F2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GUI list" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="159">
   <si>
     <t>ID</t>
   </si>
@@ -503,6 +503,9 @@
   </si>
   <si>
     <t>Trí</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -613,7 +616,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -676,6 +679,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -1183,6 +1187,9 @@
       <c r="C7" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="G7" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
@@ -1194,6 +1201,9 @@
       <c r="C8" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="G8" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="9" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
@@ -1215,6 +1225,9 @@
       <c r="D10" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="G10" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
@@ -1226,6 +1239,9 @@
       <c r="D11" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="G11" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
@@ -1237,6 +1253,9 @@
       <c r="D12" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="G12" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
@@ -1248,6 +1267,9 @@
       <c r="D13" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="G13" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="12" t="s">
@@ -1259,6 +1281,9 @@
       <c r="D14" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="G14" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
@@ -1270,6 +1295,9 @@
       <c r="D15" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="G15" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
@@ -1281,8 +1309,11 @@
       <c r="D16" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G16" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>95</v>
       </c>
@@ -1292,8 +1323,11 @@
       <c r="D17" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>96</v>
       </c>
@@ -1304,7 +1338,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>97</v>
       </c>
@@ -1315,7 +1349,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>1.3</v>
       </c>
@@ -1325,7 +1359,7 @@
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
     </row>
-    <row r="21" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>48</v>
       </c>
@@ -1335,8 +1369,11 @@
       <c r="C21" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G21" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>49</v>
       </c>
@@ -1346,8 +1383,11 @@
       <c r="C22" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>50</v>
       </c>
@@ -1357,8 +1397,11 @@
       <c r="C23" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G23" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>51</v>
       </c>
@@ -1368,8 +1411,11 @@
       <c r="D24" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G24" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>98</v>
       </c>
@@ -1379,8 +1425,11 @@
       <c r="C25" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G25" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="12" t="s">
         <v>99</v>
       </c>
@@ -1390,8 +1439,11 @@
       <c r="C26" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>100</v>
       </c>
@@ -1402,7 +1454,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>101</v>
       </c>
@@ -1412,8 +1464,11 @@
       <c r="D28" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G28" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>102</v>
       </c>
@@ -1423,8 +1478,11 @@
       <c r="D29" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G29" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>103</v>
       </c>
@@ -1435,7 +1493,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>104</v>
       </c>
@@ -1446,7 +1504,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>105</v>
       </c>
@@ -1457,7 +1515,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>106</v>
       </c>
@@ -1468,7 +1526,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>107</v>
       </c>
@@ -1479,7 +1537,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>1.4</v>
       </c>
@@ -1487,7 +1545,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:5" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="25" t="s">
         <v>108</v>
       </c>
@@ -1498,8 +1556,11 @@
         <v>138</v>
       </c>
       <c r="D36" s="10"/>
-    </row>
-    <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="G36" s="26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="25" t="s">
         <v>109</v>
       </c>
@@ -1509,8 +1570,11 @@
       <c r="C37" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="G37" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="25" t="s">
         <v>110</v>
       </c>
@@ -1520,8 +1584,11 @@
       <c r="C38" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G38" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="25" t="s">
         <v>111</v>
       </c>
@@ -1532,7 +1599,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="25" t="s">
         <v>112</v>
       </c>
@@ -1543,7 +1610,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="25" t="s">
         <v>113</v>
       </c>
@@ -1554,7 +1621,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="25" t="s">
         <v>114</v>
       </c>
@@ -1565,7 +1632,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="22">
         <v>2</v>
       </c>
@@ -1576,7 +1643,7 @@
       <c r="D43" s="23"/>
       <c r="E43" s="24"/>
     </row>
-    <row r="44" spans="1:5" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>2.1</v>
       </c>
@@ -1586,7 +1653,7 @@
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>52</v>
       </c>
@@ -1596,8 +1663,11 @@
       <c r="C45" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="G45" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>91</v>
       </c>
@@ -1608,7 +1678,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>92</v>
       </c>
@@ -1618,8 +1688,11 @@
       <c r="C47" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="G47" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>115</v>
       </c>
@@ -1630,7 +1703,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>116</v>
       </c>
@@ -1641,7 +1714,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>118</v>
       </c>
@@ -1652,7 +1725,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>121</v>
       </c>
@@ -1662,8 +1735,11 @@
       <c r="D51" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G51" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -1673,7 +1749,7 @@
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
     </row>
-    <row r="53" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="12" t="s">
         <v>53</v>
       </c>
@@ -1683,8 +1759,11 @@
       <c r="C53" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G53" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>54</v>
       </c>
@@ -1694,8 +1773,11 @@
       <c r="C54" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G54" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>122</v>
       </c>
@@ -1705,8 +1787,11 @@
       <c r="C55" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G55" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="12" t="s">
         <v>123</v>
       </c>
@@ -1716,8 +1801,11 @@
       <c r="C56" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G56" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>124</v>
       </c>
@@ -1727,8 +1815,11 @@
       <c r="C57" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G57" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>125</v>
       </c>
@@ -1738,8 +1829,11 @@
       <c r="D58" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G58" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>126</v>
       </c>
@@ -1749,8 +1843,11 @@
       <c r="C59" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G59" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="12" t="s">
         <v>127</v>
       </c>
@@ -1760,8 +1857,11 @@
       <c r="D60" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G60" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>128</v>
       </c>
@@ -1771,8 +1871,11 @@
       <c r="D61" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G61" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>129</v>
       </c>
@@ -1782,8 +1885,11 @@
       <c r="D62" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G62" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>130</v>
       </c>
@@ -1793,8 +1899,11 @@
       <c r="C63" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G63" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>131</v>
       </c>
@@ -1804,8 +1913,11 @@
       <c r="D64" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G64" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>3</v>
       </c>
@@ -1815,7 +1927,7 @@
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
     </row>
-    <row r="66" spans="1:4" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>3.1</v>
       </c>
@@ -1825,7 +1937,7 @@
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
     </row>
-    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="12" t="s">
         <v>56</v>
       </c>
@@ -1835,8 +1947,11 @@
       <c r="C67" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G67" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="12" t="s">
         <v>57</v>
       </c>
@@ -1846,8 +1961,11 @@
       <c r="D68" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G68" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
         <v>75</v>
       </c>
@@ -1857,8 +1975,11 @@
       <c r="C69" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G69" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="12" t="s">
         <v>76</v>
       </c>
@@ -1868,8 +1989,11 @@
       <c r="C70" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+      <c r="G70" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A71" s="12" t="s">
         <v>77</v>
       </c>
@@ -1879,8 +2003,11 @@
       <c r="C71" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G71" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="8">
         <v>3.2</v>
       </c>
@@ -1890,7 +2017,7 @@
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
     </row>
-    <row r="73" spans="1:4" ht="32" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="32" x14ac:dyDescent="0.2">
       <c r="A73" s="12" t="s">
         <v>60</v>
       </c>
@@ -1900,8 +2027,11 @@
       <c r="C73" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G73" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="12" t="s">
         <v>61</v>
       </c>
@@ -1911,8 +2041,11 @@
       <c r="C74" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G74" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="8">
         <v>3.3</v>
       </c>
@@ -1922,7 +2055,7 @@
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
     </row>
-    <row r="76" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="12" t="s">
         <v>64</v>
       </c>
@@ -1932,8 +2065,11 @@
       <c r="C76" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G76" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="12" t="s">
         <v>65</v>
       </c>
@@ -1943,8 +2079,11 @@
       <c r="C77" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G77" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="12" t="s">
         <v>78</v>
       </c>
@@ -1954,8 +2093,11 @@
       <c r="C78" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G78" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="12" t="s">
         <v>79</v>
       </c>
@@ -1965,8 +2107,11 @@
       <c r="C79" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="G79" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="12" t="s">
         <v>80</v>
       </c>
@@ -1975,6 +2120,9 @@
       </c>
       <c r="C80" s="7" t="s">
         <v>138</v>
+      </c>
+      <c r="G80" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/project/HW4/GUI_Checklist.xlsx
+++ b/project/HW4/GUI_Checklist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thanhthuy/Documents/Testing-PRJ-SM/project/HW4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SoftwareTesting\Testing-PRJ-SM\project\HW4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2280B1-6FE5-A142-8A3D-072E4499F2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D42DF9-25B0-43C2-890A-027F55765C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GUI list" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="159">
   <si>
     <t>ID</t>
   </si>
@@ -616,7 +616,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -679,7 +679,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -1033,15 +1032,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" customWidth="1"/>
-    <col min="3" max="3" width="33.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" customWidth="1"/>
+    <col min="3" max="3" width="33.7109375" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1055,7 +1054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="80" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1066,13 +1065,13 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
     </row>
   </sheetData>
@@ -1086,14 +1085,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J80"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="82" style="2" customWidth="1"/>
-    <col min="3" max="4" width="6.33203125" style="7" customWidth="1"/>
+    <col min="3" max="4" width="6.28515625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
@@ -1104,7 +1103,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
@@ -1115,7 +1114,7 @@
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
     </row>
-    <row r="3" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>3</v>
       </c>
@@ -1127,7 +1126,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="17"/>
     </row>
-    <row r="4" spans="1:10" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>132</v>
       </c>
@@ -1156,7 +1155,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
         <v>1</v>
       </c>
@@ -1167,7 +1166,7 @@
       <c r="D5" s="20"/>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>1.1000000000000001</v>
       </c>
@@ -1177,7 +1176,7 @@
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>41</v>
       </c>
@@ -1190,8 +1189,11 @@
       <c r="G7" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="J7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>42</v>
       </c>
@@ -1204,8 +1206,11 @@
       <c r="G8" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>1.2</v>
       </c>
@@ -1215,7 +1220,7 @@
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
     </row>
-    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>44</v>
       </c>
@@ -1228,8 +1233,11 @@
       <c r="G10" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="J10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>45</v>
       </c>
@@ -1242,8 +1250,11 @@
       <c r="G11" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="J11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>46</v>
       </c>
@@ -1256,8 +1267,11 @@
       <c r="G12" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="J12" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>47</v>
       </c>
@@ -1270,8 +1284,11 @@
       <c r="G13" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="J13" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>89</v>
       </c>
@@ -1284,8 +1301,11 @@
       <c r="G14" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="J14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>90</v>
       </c>
@@ -1298,8 +1318,11 @@
       <c r="G15" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="J15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>94</v>
       </c>
@@ -1312,8 +1335,11 @@
       <c r="G16" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J16" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>95</v>
       </c>
@@ -1326,8 +1352,11 @@
       <c r="G17" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>96</v>
       </c>
@@ -1337,8 +1366,11 @@
       <c r="D18" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J18" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>97</v>
       </c>
@@ -1348,8 +1380,11 @@
       <c r="C19" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <v>1.3</v>
       </c>
@@ -1359,7 +1394,7 @@
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
     </row>
-    <row r="21" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
         <v>48</v>
       </c>
@@ -1372,8 +1407,11 @@
       <c r="G21" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>49</v>
       </c>
@@ -1386,8 +1424,11 @@
       <c r="G22" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J22" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
         <v>50</v>
       </c>
@@ -1400,8 +1441,11 @@
       <c r="G23" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J23" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>51</v>
       </c>
@@ -1414,8 +1458,11 @@
       <c r="G24" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
         <v>98</v>
       </c>
@@ -1428,8 +1475,11 @@
       <c r="G25" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J25" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>99</v>
       </c>
@@ -1442,8 +1492,11 @@
       <c r="G26" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J26" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="s">
         <v>100</v>
       </c>
@@ -1453,8 +1506,11 @@
       <c r="C27" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J27" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>101</v>
       </c>
@@ -1467,8 +1523,11 @@
       <c r="G28" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
         <v>102</v>
       </c>
@@ -1481,8 +1540,11 @@
       <c r="G29" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>103</v>
       </c>
@@ -1492,8 +1554,11 @@
       <c r="C30" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J30" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>104</v>
       </c>
@@ -1504,7 +1569,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>105</v>
       </c>
@@ -1515,7 +1580,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="s">
         <v>106</v>
       </c>
@@ -1526,7 +1591,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>107</v>
       </c>
@@ -1537,7 +1602,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <v>1.4</v>
       </c>
@@ -1545,7 +1610,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="25" t="s">
         <v>108</v>
       </c>
@@ -1556,11 +1621,14 @@
         <v>138</v>
       </c>
       <c r="D36" s="10"/>
-      <c r="G36" s="26" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="G36" t="s">
+        <v>158</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="25" t="s">
         <v>109</v>
       </c>
@@ -1573,8 +1641,11 @@
       <c r="G37" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J37" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="25" t="s">
         <v>110</v>
       </c>
@@ -1587,8 +1658,11 @@
       <c r="G38" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J38" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="25" t="s">
         <v>111</v>
       </c>
@@ -1599,7 +1673,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="25" t="s">
         <v>112</v>
       </c>
@@ -1610,7 +1684,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="25" t="s">
         <v>113</v>
       </c>
@@ -1621,7 +1695,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="25" t="s">
         <v>114</v>
       </c>
@@ -1632,7 +1706,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="22">
         <v>2</v>
       </c>
@@ -1643,7 +1717,7 @@
       <c r="D43" s="23"/>
       <c r="E43" s="24"/>
     </row>
-    <row r="44" spans="1:7" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8">
         <v>2.1</v>
       </c>
@@ -1653,7 +1727,7 @@
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="12" t="s">
         <v>52</v>
       </c>
@@ -1666,8 +1740,11 @@
       <c r="G45" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J45" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
         <v>91</v>
       </c>
@@ -1677,8 +1754,11 @@
       <c r="C46" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J46" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="12" t="s">
         <v>92</v>
       </c>
@@ -1691,8 +1771,11 @@
       <c r="G47" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J47" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>115</v>
       </c>
@@ -1702,8 +1785,11 @@
       <c r="C48" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J48" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="12" t="s">
         <v>116</v>
       </c>
@@ -1713,8 +1799,11 @@
       <c r="C49" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="J49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>118</v>
       </c>
@@ -1724,8 +1813,11 @@
       <c r="C50" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J50" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
         <v>121</v>
       </c>
@@ -1738,8 +1830,11 @@
       <c r="G51" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J51" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -1749,7 +1844,7 @@
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
     </row>
-    <row r="53" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
         <v>53</v>
       </c>
@@ -1762,8 +1857,11 @@
       <c r="G53" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J53" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
         <v>54</v>
       </c>
@@ -1776,8 +1874,11 @@
       <c r="G54" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J54" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
         <v>122</v>
       </c>
@@ -1790,8 +1891,11 @@
       <c r="G55" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J55" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
         <v>123</v>
       </c>
@@ -1804,8 +1908,11 @@
       <c r="G56" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J56" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
         <v>124</v>
       </c>
@@ -1818,8 +1925,11 @@
       <c r="G57" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J57" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
         <v>125</v>
       </c>
@@ -1832,8 +1942,11 @@
       <c r="G58" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J58" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="12" t="s">
         <v>126</v>
       </c>
@@ -1847,7 +1960,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
         <v>127</v>
       </c>
@@ -1860,8 +1973,11 @@
       <c r="G60" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J60" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="12" t="s">
         <v>128</v>
       </c>
@@ -1874,8 +1990,11 @@
       <c r="G61" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J61" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>129</v>
       </c>
@@ -1888,8 +2007,11 @@
       <c r="G62" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J62" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
         <v>130</v>
       </c>
@@ -1902,8 +2024,11 @@
       <c r="G63" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J63" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
         <v>131</v>
       </c>
@@ -1916,8 +2041,11 @@
       <c r="G64" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J64" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8">
         <v>3</v>
       </c>
@@ -1927,7 +2055,7 @@
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
     </row>
-    <row r="66" spans="1:7" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8">
         <v>3.1</v>
       </c>
@@ -1937,7 +2065,7 @@
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
     </row>
-    <row r="67" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
         <v>56</v>
       </c>
@@ -1950,8 +2078,11 @@
       <c r="G67" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J67" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
         <v>57</v>
       </c>
@@ -1964,8 +2095,11 @@
       <c r="G68" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J68" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="12" t="s">
         <v>75</v>
       </c>
@@ -1978,8 +2112,11 @@
       <c r="G69" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J69" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
         <v>76</v>
       </c>
@@ -1992,8 +2129,11 @@
       <c r="G70" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+      <c r="J70" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="12" t="s">
         <v>77</v>
       </c>
@@ -2006,8 +2146,11 @@
       <c r="G71" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J71" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="8">
         <v>3.2</v>
       </c>
@@ -2017,7 +2160,7 @@
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
     </row>
-    <row r="73" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
         <v>60</v>
       </c>
@@ -2030,8 +2173,11 @@
       <c r="G73" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J73" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
         <v>61</v>
       </c>
@@ -2044,8 +2190,11 @@
       <c r="G74" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J74" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8">
         <v>3.3</v>
       </c>
@@ -2055,7 +2204,7 @@
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
     </row>
-    <row r="76" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
         <v>64</v>
       </c>
@@ -2068,8 +2217,11 @@
       <c r="G76" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J76" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
         <v>65</v>
       </c>
@@ -2082,8 +2234,11 @@
       <c r="G77" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J77" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
         <v>78</v>
       </c>
@@ -2096,8 +2251,11 @@
       <c r="G78" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J78" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
         <v>79</v>
       </c>
@@ -2110,8 +2268,11 @@
       <c r="G79" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J79" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
         <v>80</v>
       </c>
@@ -2123,6 +2284,9 @@
       </c>
       <c r="G80" t="s">
         <v>158</v>
+      </c>
+      <c r="J80" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/project/HW4/GUI_Checklist.xlsx
+++ b/project/HW4/GUI_Checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SoftwareTesting\Testing-PRJ-SM\project\HW4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\GitHub\Testing-PRJ-SM\project\HW4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D42DF9-25B0-43C2-890A-027F55765C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C34BD7B-6272-4939-AC19-6A7335E50059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GUI list" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="159">
   <si>
     <t>ID</t>
   </si>
@@ -1032,15 +1032,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
-    <col min="3" max="3" width="33.7109375" customWidth="1"/>
+    <col min="1" max="1" width="5.3984375" customWidth="1"/>
+    <col min="2" max="2" width="31.73046875" customWidth="1"/>
+    <col min="3" max="3" width="33.73046875" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1065,13 +1065,13 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
     </row>
   </sheetData>
@@ -1085,14 +1085,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J80"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.86328125" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="82" style="2" customWidth="1"/>
-    <col min="3" max="4" width="6.28515625" style="7" customWidth="1"/>
+    <col min="3" max="4" width="6.265625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
@@ -1103,7 +1103,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
@@ -1114,7 +1114,7 @@
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
     </row>
-    <row r="3" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="13" t="s">
         <v>3</v>
       </c>
@@ -1126,7 +1126,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="17"/>
     </row>
-    <row r="4" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A4" s="11" t="s">
         <v>132</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="18">
         <v>1</v>
       </c>
@@ -1166,7 +1166,7 @@
       <c r="D5" s="20"/>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8">
         <v>1.1000000000000001</v>
       </c>
@@ -1176,7 +1176,7 @@
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" s="12" t="s">
         <v>41</v>
       </c>
@@ -1189,11 +1189,14 @@
       <c r="G7" t="s">
         <v>158</v>
       </c>
+      <c r="H7" t="s">
+        <v>158</v>
+      </c>
       <c r="J7" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="12" t="s">
         <v>42</v>
       </c>
@@ -1206,11 +1209,14 @@
       <c r="G8" t="s">
         <v>158</v>
       </c>
+      <c r="H8" t="s">
+        <v>158</v>
+      </c>
       <c r="J8" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="8">
         <v>1.2</v>
       </c>
@@ -1220,7 +1226,7 @@
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" s="12" t="s">
         <v>44</v>
       </c>
@@ -1237,7 +1243,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" s="12" t="s">
         <v>45</v>
       </c>
@@ -1250,11 +1256,14 @@
       <c r="G11" t="s">
         <v>158</v>
       </c>
+      <c r="H11" t="s">
+        <v>158</v>
+      </c>
       <c r="J11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" s="12" t="s">
         <v>46</v>
       </c>
@@ -1267,11 +1276,14 @@
       <c r="G12" t="s">
         <v>158</v>
       </c>
+      <c r="H12" t="s">
+        <v>158</v>
+      </c>
       <c r="J12" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A13" s="12" t="s">
         <v>47</v>
       </c>
@@ -1284,11 +1296,14 @@
       <c r="G13" t="s">
         <v>158</v>
       </c>
+      <c r="H13" t="s">
+        <v>158</v>
+      </c>
       <c r="J13" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A14" s="12" t="s">
         <v>89</v>
       </c>
@@ -1301,11 +1316,14 @@
       <c r="G14" t="s">
         <v>158</v>
       </c>
+      <c r="H14" t="s">
+        <v>158</v>
+      </c>
       <c r="J14" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A15" s="12" t="s">
         <v>90</v>
       </c>
@@ -1318,11 +1336,14 @@
       <c r="G15" t="s">
         <v>158</v>
       </c>
+      <c r="H15" t="s">
+        <v>158</v>
+      </c>
       <c r="J15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A16" s="12" t="s">
         <v>94</v>
       </c>
@@ -1335,11 +1356,14 @@
       <c r="G16" t="s">
         <v>158</v>
       </c>
+      <c r="H16" t="s">
+        <v>158</v>
+      </c>
       <c r="J16" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A17" s="12" t="s">
         <v>95</v>
       </c>
@@ -1356,7 +1380,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A18" s="12" t="s">
         <v>96</v>
       </c>
@@ -1366,11 +1390,14 @@
       <c r="D18" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="H18" t="s">
+        <v>158</v>
+      </c>
       <c r="J18" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19" s="12" t="s">
         <v>97</v>
       </c>
@@ -1380,11 +1407,14 @@
       <c r="C19" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="H19" t="s">
+        <v>158</v>
+      </c>
       <c r="J19" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="8">
         <v>1.3</v>
       </c>
@@ -1394,7 +1424,7 @@
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
     </row>
-    <row r="21" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A21" s="12" t="s">
         <v>48</v>
       </c>
@@ -1407,11 +1437,14 @@
       <c r="G21" t="s">
         <v>158</v>
       </c>
+      <c r="H21" t="s">
+        <v>158</v>
+      </c>
       <c r="J21" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A22" s="12" t="s">
         <v>49</v>
       </c>
@@ -1424,11 +1457,14 @@
       <c r="G22" t="s">
         <v>158</v>
       </c>
+      <c r="H22" t="s">
+        <v>158</v>
+      </c>
       <c r="J22" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A23" s="12" t="s">
         <v>50</v>
       </c>
@@ -1445,7 +1481,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A24" s="12" t="s">
         <v>51</v>
       </c>
@@ -1458,11 +1494,14 @@
       <c r="G24" t="s">
         <v>158</v>
       </c>
+      <c r="H24" t="s">
+        <v>158</v>
+      </c>
       <c r="J24" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A25" s="12" t="s">
         <v>98</v>
       </c>
@@ -1475,11 +1514,14 @@
       <c r="G25" t="s">
         <v>158</v>
       </c>
+      <c r="H25" t="s">
+        <v>158</v>
+      </c>
       <c r="J25" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A26" s="12" t="s">
         <v>99</v>
       </c>
@@ -1492,11 +1534,14 @@
       <c r="G26" t="s">
         <v>158</v>
       </c>
+      <c r="H26" t="s">
+        <v>158</v>
+      </c>
       <c r="J26" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A27" s="12" t="s">
         <v>100</v>
       </c>
@@ -1506,11 +1551,14 @@
       <c r="C27" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="H27" t="s">
+        <v>158</v>
+      </c>
       <c r="J27" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A28" s="12" t="s">
         <v>101</v>
       </c>
@@ -1523,11 +1571,14 @@
       <c r="G28" t="s">
         <v>158</v>
       </c>
+      <c r="H28" t="s">
+        <v>158</v>
+      </c>
       <c r="J28" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A29" s="12" t="s">
         <v>102</v>
       </c>
@@ -1544,7 +1595,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A30" s="12" t="s">
         <v>103</v>
       </c>
@@ -1558,7 +1609,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A31" s="12" t="s">
         <v>104</v>
       </c>
@@ -1569,7 +1620,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A32" s="12" t="s">
         <v>105</v>
       </c>
@@ -1580,7 +1631,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A33" s="12" t="s">
         <v>106</v>
       </c>
@@ -1591,7 +1642,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A34" s="12" t="s">
         <v>107</v>
       </c>
@@ -1602,7 +1653,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="8">
         <v>1.4</v>
       </c>
@@ -1610,7 +1661,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="25" t="s">
         <v>108</v>
       </c>
@@ -1628,7 +1679,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A37" s="25" t="s">
         <v>109</v>
       </c>
@@ -1645,7 +1696,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A38" s="25" t="s">
         <v>110</v>
       </c>
@@ -1662,7 +1713,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A39" s="25" t="s">
         <v>111</v>
       </c>
@@ -1673,7 +1724,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A40" s="25" t="s">
         <v>112</v>
       </c>
@@ -1684,7 +1735,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A41" s="25" t="s">
         <v>113</v>
       </c>
@@ -1695,7 +1746,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A42" s="25" t="s">
         <v>114</v>
       </c>
@@ -1706,7 +1757,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="22">
         <v>2</v>
       </c>
@@ -1717,7 +1768,7 @@
       <c r="D43" s="23"/>
       <c r="E43" s="24"/>
     </row>
-    <row r="44" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="8">
         <v>2.1</v>
       </c>
@@ -1727,7 +1778,7 @@
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A45" s="12" t="s">
         <v>52</v>
       </c>
@@ -1740,11 +1791,14 @@
       <c r="G45" t="s">
         <v>158</v>
       </c>
+      <c r="H45" t="s">
+        <v>158</v>
+      </c>
       <c r="J45" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A46" s="12" t="s">
         <v>91</v>
       </c>
@@ -1754,11 +1808,14 @@
       <c r="C46" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="H46" t="s">
+        <v>158</v>
+      </c>
       <c r="J46" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A47" s="12" t="s">
         <v>92</v>
       </c>
@@ -1771,11 +1828,14 @@
       <c r="G47" t="s">
         <v>158</v>
       </c>
+      <c r="H47" t="s">
+        <v>158</v>
+      </c>
       <c r="J47" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A48" s="12" t="s">
         <v>115</v>
       </c>
@@ -1789,7 +1849,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A49" s="12" t="s">
         <v>116</v>
       </c>
@@ -1803,7 +1863,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A50" s="12" t="s">
         <v>118</v>
       </c>
@@ -1817,7 +1877,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A51" s="12" t="s">
         <v>121</v>
       </c>
@@ -1834,7 +1894,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -1844,7 +1904,7 @@
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A53" s="12" t="s">
         <v>53</v>
       </c>
@@ -1857,11 +1917,14 @@
       <c r="G53" t="s">
         <v>158</v>
       </c>
+      <c r="H53" t="s">
+        <v>158</v>
+      </c>
       <c r="J53" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A54" s="12" t="s">
         <v>54</v>
       </c>
@@ -1874,11 +1937,14 @@
       <c r="G54" t="s">
         <v>158</v>
       </c>
+      <c r="H54" t="s">
+        <v>158</v>
+      </c>
       <c r="J54" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A55" s="12" t="s">
         <v>122</v>
       </c>
@@ -1895,7 +1961,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A56" s="12" t="s">
         <v>123</v>
       </c>
@@ -1908,11 +1974,14 @@
       <c r="G56" t="s">
         <v>158</v>
       </c>
+      <c r="H56" t="s">
+        <v>158</v>
+      </c>
       <c r="J56" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A57" s="12" t="s">
         <v>124</v>
       </c>
@@ -1929,7 +1998,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A58" s="12" t="s">
         <v>125</v>
       </c>
@@ -1942,11 +2011,14 @@
       <c r="G58" t="s">
         <v>158</v>
       </c>
+      <c r="H58" t="s">
+        <v>158</v>
+      </c>
       <c r="J58" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A59" s="12" t="s">
         <v>126</v>
       </c>
@@ -1960,7 +2032,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A60" s="12" t="s">
         <v>127</v>
       </c>
@@ -1973,11 +2045,14 @@
       <c r="G60" t="s">
         <v>158</v>
       </c>
+      <c r="H60" t="s">
+        <v>158</v>
+      </c>
       <c r="J60" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A61" s="12" t="s">
         <v>128</v>
       </c>
@@ -1990,11 +2065,14 @@
       <c r="G61" t="s">
         <v>158</v>
       </c>
+      <c r="H61" t="s">
+        <v>158</v>
+      </c>
       <c r="J61" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A62" s="12" t="s">
         <v>129</v>
       </c>
@@ -2011,7 +2089,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A63" s="12" t="s">
         <v>130</v>
       </c>
@@ -2028,7 +2106,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A64" s="12" t="s">
         <v>131</v>
       </c>
@@ -2045,7 +2123,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="8">
         <v>3</v>
       </c>
@@ -2055,7 +2133,7 @@
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
     </row>
-    <row r="66" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="8">
         <v>3.1</v>
       </c>
@@ -2065,7 +2143,7 @@
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
     </row>
-    <row r="67" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A67" s="12" t="s">
         <v>56</v>
       </c>
@@ -2082,7 +2160,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A68" s="12" t="s">
         <v>57</v>
       </c>
@@ -2099,7 +2177,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A69" s="12" t="s">
         <v>75</v>
       </c>
@@ -2116,7 +2194,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A70" s="12" t="s">
         <v>76</v>
       </c>
@@ -2133,7 +2211,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A71" s="12" t="s">
         <v>77</v>
       </c>
@@ -2150,7 +2228,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="72" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="8">
         <v>3.2</v>
       </c>
@@ -2160,7 +2238,7 @@
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
     </row>
-    <row r="73" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A73" s="12" t="s">
         <v>60</v>
       </c>
@@ -2177,7 +2255,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A74" s="12" t="s">
         <v>61</v>
       </c>
@@ -2194,7 +2272,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="8">
         <v>3.3</v>
       </c>
@@ -2204,7 +2282,7 @@
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A76" s="12" t="s">
         <v>64</v>
       </c>
@@ -2221,7 +2299,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A77" s="12" t="s">
         <v>65</v>
       </c>
@@ -2238,7 +2316,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A78" s="12" t="s">
         <v>78</v>
       </c>
@@ -2255,7 +2333,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A79" s="12" t="s">
         <v>79</v>
       </c>
@@ -2272,7 +2350,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A80" s="12" t="s">
         <v>80</v>
       </c>

--- a/project/HW4/GUI_Checklist.xlsx
+++ b/project/HW4/GUI_Checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\GitHub\Testing-PRJ-SM\project\HW4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viett\OneDrive\Documents\GitHub\Testing-PRJ-SM\project\HW4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C34BD7B-6272-4939-AC19-6A7335E50059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7740A8-AC78-414D-9C37-E2B00D2BEB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GUI list" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="159">
   <si>
     <t>ID</t>
   </si>
@@ -1032,15 +1032,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.3984375" customWidth="1"/>
-    <col min="2" max="2" width="31.73046875" customWidth="1"/>
-    <col min="3" max="3" width="33.73046875" customWidth="1"/>
+    <col min="1" max="1" width="5.44140625" customWidth="1"/>
+    <col min="2" max="2" width="31.77734375" customWidth="1"/>
+    <col min="3" max="3" width="33.77734375" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1065,13 +1065,13 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
     </row>
   </sheetData>
@@ -1085,14 +1085,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J80"/>
-  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="82" style="2" customWidth="1"/>
-    <col min="3" max="4" width="6.265625" style="7" customWidth="1"/>
+    <col min="3" max="4" width="6.21875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
@@ -1103,7 +1103,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
@@ -1114,7 +1114,7 @@
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
     </row>
-    <row r="3" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>3</v>
       </c>
@@ -1126,7 +1126,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="17"/>
     </row>
-    <row r="4" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>132</v>
       </c>
@@ -1155,7 +1155,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>1</v>
       </c>
@@ -1166,7 +1166,7 @@
       <c r="D5" s="20"/>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>1.1000000000000001</v>
       </c>
@@ -1176,7 +1176,7 @@
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>41</v>
       </c>
@@ -1192,11 +1192,14 @@
       <c r="H7" t="s">
         <v>158</v>
       </c>
+      <c r="I7" t="s">
+        <v>158</v>
+      </c>
       <c r="J7" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>42</v>
       </c>
@@ -1212,11 +1215,14 @@
       <c r="H8" t="s">
         <v>158</v>
       </c>
+      <c r="I8" t="s">
+        <v>158</v>
+      </c>
       <c r="J8" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>1.2</v>
       </c>
@@ -1226,7 +1232,7 @@
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>44</v>
       </c>
@@ -1239,11 +1245,14 @@
       <c r="G10" t="s">
         <v>158</v>
       </c>
+      <c r="I10" t="s">
+        <v>158</v>
+      </c>
       <c r="J10" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>45</v>
       </c>
@@ -1259,11 +1268,14 @@
       <c r="H11" t="s">
         <v>158</v>
       </c>
+      <c r="I11" t="s">
+        <v>158</v>
+      </c>
       <c r="J11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>46</v>
       </c>
@@ -1279,11 +1291,14 @@
       <c r="H12" t="s">
         <v>158</v>
       </c>
+      <c r="I12" t="s">
+        <v>158</v>
+      </c>
       <c r="J12" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>47</v>
       </c>
@@ -1299,11 +1314,14 @@
       <c r="H13" t="s">
         <v>158</v>
       </c>
+      <c r="I13" t="s">
+        <v>158</v>
+      </c>
       <c r="J13" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>89</v>
       </c>
@@ -1319,11 +1337,14 @@
       <c r="H14" t="s">
         <v>158</v>
       </c>
+      <c r="I14" t="s">
+        <v>158</v>
+      </c>
       <c r="J14" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>90</v>
       </c>
@@ -1339,11 +1360,14 @@
       <c r="H15" t="s">
         <v>158</v>
       </c>
+      <c r="I15" t="s">
+        <v>158</v>
+      </c>
       <c r="J15" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>94</v>
       </c>
@@ -1359,11 +1383,14 @@
       <c r="H16" t="s">
         <v>158</v>
       </c>
+      <c r="I16" t="s">
+        <v>158</v>
+      </c>
       <c r="J16" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>95</v>
       </c>
@@ -1376,11 +1403,14 @@
       <c r="G17" t="s">
         <v>158</v>
       </c>
+      <c r="I17" t="s">
+        <v>158</v>
+      </c>
       <c r="J17" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>96</v>
       </c>
@@ -1393,11 +1423,14 @@
       <c r="H18" t="s">
         <v>158</v>
       </c>
+      <c r="I18" t="s">
+        <v>158</v>
+      </c>
       <c r="J18" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>97</v>
       </c>
@@ -1410,11 +1443,14 @@
       <c r="H19" t="s">
         <v>158</v>
       </c>
+      <c r="I19" t="s">
+        <v>158</v>
+      </c>
       <c r="J19" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>1.3</v>
       </c>
@@ -1424,7 +1460,7 @@
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
     </row>
-    <row r="21" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
         <v>48</v>
       </c>
@@ -1440,11 +1476,14 @@
       <c r="H21" t="s">
         <v>158</v>
       </c>
+      <c r="I21" t="s">
+        <v>158</v>
+      </c>
       <c r="J21" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>49</v>
       </c>
@@ -1460,11 +1499,14 @@
       <c r="H22" t="s">
         <v>158</v>
       </c>
+      <c r="I22" t="s">
+        <v>158</v>
+      </c>
       <c r="J22" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>50</v>
       </c>
@@ -1477,11 +1519,14 @@
       <c r="G23" t="s">
         <v>158</v>
       </c>
+      <c r="I23" t="s">
+        <v>158</v>
+      </c>
       <c r="J23" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>51</v>
       </c>
@@ -1497,11 +1542,14 @@
       <c r="H24" t="s">
         <v>158</v>
       </c>
+      <c r="I24" t="s">
+        <v>158</v>
+      </c>
       <c r="J24" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>98</v>
       </c>
@@ -1517,11 +1565,14 @@
       <c r="H25" t="s">
         <v>158</v>
       </c>
+      <c r="I25" t="s">
+        <v>158</v>
+      </c>
       <c r="J25" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>99</v>
       </c>
@@ -1537,11 +1588,14 @@
       <c r="H26" t="s">
         <v>158</v>
       </c>
+      <c r="I26" t="s">
+        <v>158</v>
+      </c>
       <c r="J26" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>100</v>
       </c>
@@ -1554,11 +1608,14 @@
       <c r="H27" t="s">
         <v>158</v>
       </c>
+      <c r="I27" t="s">
+        <v>158</v>
+      </c>
       <c r="J27" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>101</v>
       </c>
@@ -1574,11 +1631,14 @@
       <c r="H28" t="s">
         <v>158</v>
       </c>
+      <c r="I28" t="s">
+        <v>158</v>
+      </c>
       <c r="J28" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>102</v>
       </c>
@@ -1591,11 +1651,14 @@
       <c r="G29" t="s">
         <v>158</v>
       </c>
+      <c r="I29" t="s">
+        <v>158</v>
+      </c>
       <c r="J29" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
         <v>103</v>
       </c>
@@ -1609,7 +1672,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="12" t="s">
         <v>104</v>
       </c>
@@ -1619,8 +1682,11 @@
       <c r="C31" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="I31" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>105</v>
       </c>
@@ -1630,8 +1696,11 @@
       <c r="C32" s="7" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="I32" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="12" t="s">
         <v>106</v>
       </c>
@@ -1642,7 +1711,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
         <v>107</v>
       </c>
@@ -1653,7 +1722,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>1.4</v>
       </c>
@@ -1661,7 +1730,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="25" t="s">
         <v>108</v>
       </c>
@@ -1679,7 +1748,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="25" t="s">
         <v>109</v>
       </c>
@@ -1696,7 +1765,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="25" t="s">
         <v>110</v>
       </c>
@@ -1713,7 +1782,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="25" t="s">
         <v>111</v>
       </c>
@@ -1724,7 +1793,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="25" t="s">
         <v>112</v>
       </c>
@@ -1735,7 +1804,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="25" t="s">
         <v>113</v>
       </c>
@@ -1746,7 +1815,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="25" t="s">
         <v>114</v>
       </c>
@@ -1757,7 +1826,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="22">
         <v>2</v>
       </c>
@@ -1768,7 +1837,7 @@
       <c r="D43" s="23"/>
       <c r="E43" s="24"/>
     </row>
-    <row r="44" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8">
         <v>2.1</v>
       </c>
@@ -1778,7 +1847,7 @@
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="12" t="s">
         <v>52</v>
       </c>
@@ -1794,11 +1863,14 @@
       <c r="H45" t="s">
         <v>158</v>
       </c>
+      <c r="I45" t="s">
+        <v>158</v>
+      </c>
       <c r="J45" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
         <v>91</v>
       </c>
@@ -1811,11 +1883,14 @@
       <c r="H46" t="s">
         <v>158</v>
       </c>
+      <c r="I46" t="s">
+        <v>158</v>
+      </c>
       <c r="J46" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="12" t="s">
         <v>92</v>
       </c>
@@ -1831,11 +1906,14 @@
       <c r="H47" t="s">
         <v>158</v>
       </c>
+      <c r="I47" t="s">
+        <v>158</v>
+      </c>
       <c r="J47" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>115</v>
       </c>
@@ -1849,7 +1927,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="12" t="s">
         <v>116</v>
       </c>
@@ -1863,7 +1941,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
         <v>118</v>
       </c>
@@ -1877,7 +1955,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="12" t="s">
         <v>121</v>
       </c>
@@ -1894,7 +1972,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -1904,7 +1982,7 @@
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="12" t="s">
         <v>53</v>
       </c>
@@ -1920,11 +1998,14 @@
       <c r="H53" t="s">
         <v>158</v>
       </c>
+      <c r="I53" t="s">
+        <v>158</v>
+      </c>
       <c r="J53" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
         <v>54</v>
       </c>
@@ -1940,11 +2021,14 @@
       <c r="H54" t="s">
         <v>158</v>
       </c>
+      <c r="I54" t="s">
+        <v>158</v>
+      </c>
       <c r="J54" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="12" t="s">
         <v>122</v>
       </c>
@@ -1957,11 +2041,14 @@
       <c r="G55" t="s">
         <v>158</v>
       </c>
+      <c r="I55" t="s">
+        <v>158</v>
+      </c>
       <c r="J55" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>123</v>
       </c>
@@ -1977,11 +2064,14 @@
       <c r="H56" t="s">
         <v>158</v>
       </c>
+      <c r="I56" t="s">
+        <v>158</v>
+      </c>
       <c r="J56" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="12" t="s">
         <v>124</v>
       </c>
@@ -1994,11 +2084,14 @@
       <c r="G57" t="s">
         <v>158</v>
       </c>
+      <c r="I57" t="s">
+        <v>158</v>
+      </c>
       <c r="J57" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
         <v>125</v>
       </c>
@@ -2014,11 +2107,14 @@
       <c r="H58" t="s">
         <v>158</v>
       </c>
+      <c r="I58" t="s">
+        <v>158</v>
+      </c>
       <c r="J58" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="12" t="s">
         <v>126</v>
       </c>
@@ -2031,8 +2127,11 @@
       <c r="G59" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="I59" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
         <v>127</v>
       </c>
@@ -2048,11 +2147,14 @@
       <c r="H60" t="s">
         <v>158</v>
       </c>
+      <c r="I60" t="s">
+        <v>158</v>
+      </c>
       <c r="J60" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="12" t="s">
         <v>128</v>
       </c>
@@ -2068,11 +2170,14 @@
       <c r="H61" t="s">
         <v>158</v>
       </c>
+      <c r="I61" t="s">
+        <v>158</v>
+      </c>
       <c r="J61" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
         <v>129</v>
       </c>
@@ -2085,11 +2190,14 @@
       <c r="G62" t="s">
         <v>158</v>
       </c>
+      <c r="I62" t="s">
+        <v>158</v>
+      </c>
       <c r="J62" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="12" t="s">
         <v>130</v>
       </c>
@@ -2102,11 +2210,14 @@
       <c r="G63" t="s">
         <v>158</v>
       </c>
+      <c r="I63" t="s">
+        <v>158</v>
+      </c>
       <c r="J63" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
         <v>131</v>
       </c>
@@ -2119,11 +2230,14 @@
       <c r="G64" t="s">
         <v>158</v>
       </c>
+      <c r="I64" t="s">
+        <v>158</v>
+      </c>
       <c r="J64" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8">
         <v>3</v>
       </c>
@@ -2133,7 +2247,7 @@
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
     </row>
-    <row r="66" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8">
         <v>3.1</v>
       </c>
@@ -2143,7 +2257,7 @@
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="12" t="s">
         <v>56</v>
       </c>
@@ -2156,11 +2270,14 @@
       <c r="G67" t="s">
         <v>158</v>
       </c>
+      <c r="I67" t="s">
+        <v>158</v>
+      </c>
       <c r="J67" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
         <v>57</v>
       </c>
@@ -2173,11 +2290,14 @@
       <c r="G68" t="s">
         <v>158</v>
       </c>
+      <c r="I68" t="s">
+        <v>158</v>
+      </c>
       <c r="J68" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="12" t="s">
         <v>75</v>
       </c>
@@ -2190,11 +2310,14 @@
       <c r="G69" t="s">
         <v>158</v>
       </c>
+      <c r="I69" t="s">
+        <v>158</v>
+      </c>
       <c r="J69" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>76</v>
       </c>
@@ -2211,7 +2334,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="12" t="s">
         <v>77</v>
       </c>
@@ -2224,11 +2347,14 @@
       <c r="G71" t="s">
         <v>158</v>
       </c>
+      <c r="I71" t="s">
+        <v>158</v>
+      </c>
       <c r="J71" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="72" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:10" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8">
         <v>3.2</v>
       </c>
@@ -2238,7 +2364,7 @@
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
     </row>
-    <row r="73" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="12" t="s">
         <v>60</v>
       </c>
@@ -2255,7 +2381,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
         <v>61</v>
       </c>
@@ -2272,7 +2398,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="6" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:10" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8">
         <v>3.3</v>
       </c>
@@ -2282,7 +2408,7 @@
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>64</v>
       </c>
@@ -2299,7 +2425,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="12" t="s">
         <v>65</v>
       </c>
@@ -2316,7 +2442,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>78</v>
       </c>
@@ -2333,7 +2459,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="12" t="s">
         <v>79</v>
       </c>
@@ -2350,7 +2476,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
         <v>80</v>
       </c>

--- a/project/HW4/GUI_Checklist.xlsx
+++ b/project/HW4/GUI_Checklist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10714"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viett\OneDrive\Documents\GitHub\Testing-PRJ-SM\project\HW4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thanhthuy/Documents/Testing-PRJ-SM/project/HW4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7740A8-AC78-414D-9C37-E2B00D2BEB35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CA72CA4-43F4-154C-AA4A-E12B6BB44CA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GUI list" sheetId="2" r:id="rId1"/>
@@ -558,7 +558,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -574,6 +574,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -616,7 +622,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -678,6 +684,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -1032,15 +1051,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" customWidth="1"/>
-    <col min="2" max="2" width="31.77734375" customWidth="1"/>
-    <col min="3" max="3" width="33.77734375" customWidth="1"/>
+    <col min="1" max="1" width="5.5" customWidth="1"/>
+    <col min="2" max="2" width="31.83203125" customWidth="1"/>
+    <col min="3" max="3" width="33.83203125" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1054,7 +1073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="80" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -1065,13 +1084,13 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
     </row>
   </sheetData>
@@ -1085,14 +1104,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J80"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" style="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="82" style="2" customWidth="1"/>
-    <col min="3" max="4" width="6.21875" style="7" customWidth="1"/>
+    <col min="3" max="4" width="6.1640625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>4</v>
       </c>
@@ -1103,7 +1122,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="2" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
         <v>5</v>
       </c>
@@ -1114,7 +1133,7 @@
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
     </row>
-    <row r="3" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="13" t="s">
         <v>3</v>
       </c>
@@ -1126,7 +1145,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="17"/>
     </row>
-    <row r="4" spans="1:10" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
         <v>132</v>
       </c>
@@ -1155,7 +1174,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="18">
         <v>1</v>
       </c>
@@ -1166,7 +1185,7 @@
       <c r="D5" s="20"/>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>1.1000000000000001</v>
       </c>
@@ -1176,53 +1195,59 @@
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G7" t="s">
-        <v>158</v>
-      </c>
-      <c r="H7" t="s">
-        <v>158</v>
-      </c>
-      <c r="I7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="C7" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="28"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H7" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I7" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A8" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G8" t="s">
-        <v>158</v>
-      </c>
-      <c r="H8" t="s">
-        <v>158</v>
-      </c>
-      <c r="I8" t="s">
-        <v>158</v>
-      </c>
-      <c r="J8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D8" s="28"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H8" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I8" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>1.2</v>
       </c>
@@ -1232,7 +1257,7 @@
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>44</v>
       </c>
@@ -1252,145 +1277,163 @@
         <v>138</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G11" t="s">
-        <v>158</v>
-      </c>
-      <c r="H11" t="s">
-        <v>158</v>
-      </c>
-      <c r="I11" t="s">
-        <v>158</v>
-      </c>
-      <c r="J11" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+      <c r="C11" s="28"/>
+      <c r="D11" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I11" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J11" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G12" t="s">
-        <v>158</v>
-      </c>
-      <c r="H12" t="s">
-        <v>158</v>
-      </c>
-      <c r="I12" t="s">
-        <v>158</v>
-      </c>
-      <c r="J12" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+      <c r="C12" s="28"/>
+      <c r="D12" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H12" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I12" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J12" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G13" t="s">
-        <v>158</v>
-      </c>
-      <c r="H13" t="s">
-        <v>158</v>
-      </c>
-      <c r="I13" t="s">
-        <v>158</v>
-      </c>
-      <c r="J13" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+      <c r="C13" s="28"/>
+      <c r="D13" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H13" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J13" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G14" t="s">
-        <v>158</v>
-      </c>
-      <c r="H14" t="s">
-        <v>158</v>
-      </c>
-      <c r="I14" t="s">
-        <v>158</v>
-      </c>
-      <c r="J14" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H14" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I14" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J14" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G15" t="s">
-        <v>158</v>
-      </c>
-      <c r="H15" t="s">
-        <v>158</v>
-      </c>
-      <c r="I15" t="s">
-        <v>158</v>
-      </c>
-      <c r="J15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
+      <c r="C15" s="28"/>
+      <c r="D15" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H15" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J15" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G16" t="s">
-        <v>158</v>
-      </c>
-      <c r="H16" t="s">
-        <v>158</v>
-      </c>
-      <c r="I16" t="s">
-        <v>158</v>
-      </c>
-      <c r="J16" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="28"/>
+      <c r="D16" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H16" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J16" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>95</v>
       </c>
@@ -1410,7 +1453,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="12" t="s">
         <v>96</v>
       </c>
@@ -1430,7 +1473,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>97</v>
       </c>
@@ -1450,7 +1493,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>1.3</v>
       </c>
@@ -1460,53 +1503,59 @@
       <c r="C20" s="10"/>
       <c r="D20" s="10"/>
     </row>
-    <row r="21" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
+    <row r="21" spans="1:10" ht="32" x14ac:dyDescent="0.2">
+      <c r="A21" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G21" t="s">
-        <v>158</v>
-      </c>
-      <c r="H21" t="s">
-        <v>158</v>
-      </c>
-      <c r="I21" t="s">
-        <v>158</v>
-      </c>
-      <c r="J21" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
+      <c r="C21" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="28"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H21" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I21" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J21" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="C22" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G22" t="s">
-        <v>158</v>
-      </c>
-      <c r="H22" t="s">
-        <v>158</v>
-      </c>
-      <c r="I22" t="s">
-        <v>158</v>
-      </c>
-      <c r="J22" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H22" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I22" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J22" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>50</v>
       </c>
@@ -1526,76 +1575,85 @@
         <v>138</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
+    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G24" t="s">
-        <v>158</v>
-      </c>
-      <c r="H24" t="s">
-        <v>158</v>
-      </c>
-      <c r="I24" t="s">
-        <v>158</v>
-      </c>
-      <c r="J24" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
+      <c r="C24" s="28"/>
+      <c r="D24" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H24" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I24" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J24" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G25" t="s">
-        <v>158</v>
-      </c>
-      <c r="H25" t="s">
-        <v>158</v>
-      </c>
-      <c r="I25" t="s">
-        <v>158</v>
-      </c>
-      <c r="J25" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
+      <c r="C25" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D25" s="28"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H25" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I25" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J25" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G26" t="s">
-        <v>158</v>
-      </c>
-      <c r="H26" t="s">
-        <v>158</v>
-      </c>
-      <c r="I26" t="s">
-        <v>158</v>
-      </c>
-      <c r="J26" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H26" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I26" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J26" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>100</v>
       </c>
@@ -1615,30 +1673,33 @@
         <v>138</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="12" t="s">
+    <row r="28" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G28" t="s">
-        <v>158</v>
-      </c>
-      <c r="H28" t="s">
-        <v>158</v>
-      </c>
-      <c r="I28" t="s">
-        <v>158</v>
-      </c>
-      <c r="J28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="28"/>
+      <c r="D28" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H28" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I28" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J28" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="12" t="s">
         <v>102</v>
       </c>
@@ -1658,7 +1719,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>103</v>
       </c>
@@ -1672,7 +1733,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>104</v>
       </c>
@@ -1686,7 +1747,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>105</v>
       </c>
@@ -1700,7 +1761,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" s="12" t="s">
         <v>106</v>
       </c>
@@ -1711,7 +1772,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="12" t="s">
         <v>107</v>
       </c>
@@ -1722,7 +1783,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>1.4</v>
       </c>
@@ -1730,7 +1791,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" s="6" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="25" t="s">
         <v>108</v>
       </c>
@@ -1748,7 +1809,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="25" t="s">
         <v>109</v>
       </c>
@@ -1765,7 +1826,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="25" t="s">
         <v>110</v>
       </c>
@@ -1782,7 +1843,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="25" t="s">
         <v>111</v>
       </c>
@@ -1793,7 +1854,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="25" t="s">
         <v>112</v>
       </c>
@@ -1804,7 +1865,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="25" t="s">
         <v>113</v>
       </c>
@@ -1815,7 +1876,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="25" t="s">
         <v>114</v>
       </c>
@@ -1826,7 +1887,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="22">
         <v>2</v>
       </c>
@@ -1837,7 +1898,7 @@
       <c r="D43" s="23"/>
       <c r="E43" s="24"/>
     </row>
-    <row r="44" spans="1:10" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>2.1</v>
       </c>
@@ -1847,30 +1908,33 @@
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A45" s="12" t="s">
+    <row r="45" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G45" t="s">
-        <v>158</v>
-      </c>
-      <c r="H45" t="s">
-        <v>158</v>
-      </c>
-      <c r="I45" t="s">
-        <v>158</v>
-      </c>
-      <c r="J45" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C45" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D45" s="28"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H45" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I45" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J45" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
         <v>91</v>
       </c>
@@ -1890,30 +1954,33 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="12" t="s">
+    <row r="47" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="C47" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G47" t="s">
-        <v>158</v>
-      </c>
-      <c r="H47" t="s">
-        <v>158</v>
-      </c>
-      <c r="I47" t="s">
-        <v>158</v>
-      </c>
-      <c r="J47" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C47" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D47" s="28"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H47" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I47" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J47" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>115</v>
       </c>
@@ -1927,7 +1994,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="12" t="s">
         <v>116</v>
       </c>
@@ -1941,7 +2008,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>118</v>
       </c>
@@ -1955,7 +2022,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>121</v>
       </c>
@@ -1972,7 +2039,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="52" spans="1:10" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>2.2000000000000002</v>
       </c>
@@ -1982,53 +2049,59 @@
       <c r="C52" s="10"/>
       <c r="D52" s="10"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="12" t="s">
+    <row r="53" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A53" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="C53" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G53" t="s">
-        <v>158</v>
-      </c>
-      <c r="H53" t="s">
-        <v>158</v>
-      </c>
-      <c r="I53" t="s">
-        <v>158</v>
-      </c>
-      <c r="J53" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="12" t="s">
+      <c r="C53" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D53" s="28"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H53" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I53" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J53" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="C54" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G54" t="s">
-        <v>158</v>
-      </c>
-      <c r="H54" t="s">
-        <v>158</v>
-      </c>
-      <c r="I54" t="s">
-        <v>158</v>
-      </c>
-      <c r="J54" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C54" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D54" s="28"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H54" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I54" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J54" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="12" t="s">
         <v>122</v>
       </c>
@@ -2048,30 +2121,33 @@
         <v>138</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="12" t="s">
+    <row r="56" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C56" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G56" t="s">
-        <v>158</v>
-      </c>
-      <c r="H56" t="s">
-        <v>158</v>
-      </c>
-      <c r="I56" t="s">
-        <v>158</v>
-      </c>
-      <c r="J56" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C56" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D56" s="28"/>
+      <c r="E56" s="29"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H56" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I56" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J56" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>124</v>
       </c>
@@ -2091,30 +2167,33 @@
         <v>138</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="12" t="s">
+    <row r="58" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="26" t="s">
         <v>125</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="D58" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G58" t="s">
-        <v>158</v>
-      </c>
-      <c r="H58" t="s">
-        <v>158</v>
-      </c>
-      <c r="I58" t="s">
-        <v>158</v>
-      </c>
-      <c r="J58" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C58" s="28"/>
+      <c r="D58" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H58" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I58" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J58" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="12" t="s">
         <v>126</v>
       </c>
@@ -2131,53 +2210,59 @@
         <v>158</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A60" s="12" t="s">
+    <row r="60" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="D60" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G60" t="s">
-        <v>158</v>
-      </c>
-      <c r="H60" t="s">
-        <v>158</v>
-      </c>
-      <c r="I60" t="s">
-        <v>158</v>
-      </c>
-      <c r="J60" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A61" s="12" t="s">
+      <c r="C60" s="28"/>
+      <c r="D60" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E60" s="29"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H60" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I60" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J60" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A61" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="D61" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="G61" t="s">
-        <v>158</v>
-      </c>
-      <c r="H61" t="s">
-        <v>158</v>
-      </c>
-      <c r="I61" t="s">
-        <v>158</v>
-      </c>
-      <c r="J61" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C61" s="28"/>
+      <c r="D61" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="H61" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="I61" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="J61" s="29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>129</v>
       </c>
@@ -2197,7 +2282,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="12" t="s">
         <v>130</v>
       </c>
@@ -2217,7 +2302,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>131</v>
       </c>
@@ -2237,7 +2322,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>3</v>
       </c>
@@ -2247,7 +2332,7 @@
       <c r="C65" s="10"/>
       <c r="D65" s="10"/>
     </row>
-    <row r="66" spans="1:10" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>3.1</v>
       </c>
@@ -2257,7 +2342,7 @@
       <c r="C66" s="10"/>
       <c r="D66" s="10"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="12" t="s">
         <v>56</v>
       </c>
@@ -2277,7 +2362,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="12" t="s">
         <v>57</v>
       </c>
@@ -2297,7 +2382,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="12" t="s">
         <v>75</v>
       </c>
@@ -2317,7 +2402,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="12" t="s">
         <v>76</v>
       </c>
@@ -2334,7 +2419,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A71" s="12" t="s">
         <v>77</v>
       </c>
@@ -2354,7 +2439,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="72" spans="1:10" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="8">
         <v>3.2</v>
       </c>
@@ -2364,7 +2449,7 @@
       <c r="C72" s="10"/>
       <c r="D72" s="10"/>
     </row>
-    <row r="73" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" ht="32" x14ac:dyDescent="0.2">
       <c r="A73" s="12" t="s">
         <v>60</v>
       </c>
@@ -2381,7 +2466,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="12" t="s">
         <v>61</v>
       </c>
@@ -2398,7 +2483,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="75" spans="1:10" s="6" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" s="6" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="8">
         <v>3.3</v>
       </c>
@@ -2408,7 +2493,7 @@
       <c r="C75" s="10"/>
       <c r="D75" s="10"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="12" t="s">
         <v>64</v>
       </c>
@@ -2425,7 +2510,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="12" t="s">
         <v>65</v>
       </c>
@@ -2442,7 +2527,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="12" t="s">
         <v>78</v>
       </c>
@@ -2459,7 +2544,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="12" t="s">
         <v>79</v>
       </c>
@@ -2476,7 +2561,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="12" t="s">
         <v>80</v>
       </c>
